--- a/04_DESIGN_TABLES/DesignTable_1405.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1405.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1543,24 +1548,53 @@
           <t>1405-04-06</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.675</v>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>1405-04-06</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1/4-18 (A NPTF) x 3/8-18 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1405-04-06.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 a5f51518eabc3b1f...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1571,6 +1605,11 @@
       <c r="P20" t="inlineStr">
         <is>
           <t>1405-04-06</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>OMI-DRAWING</t>
         </is>
       </c>
     </row>
@@ -1580,24 +1619,53 @@
           <t>1405-08-12</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.05</v>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>1405-08-12</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1/2-14 (A NPTF) x 3/4-14 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1405-08-12.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 3bfe55d41c442cdb...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1608,6 +1676,11 @@
       <c r="P21" t="inlineStr">
         <is>
           <t>1405-08-12</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>OMI-DRAWING</t>
         </is>
       </c>
     </row>
